--- a/Documentos Base/Sprint 2 documentacion/Sprint_02_Backlog_ICARO.xlsx
+++ b/Documentos Base/Sprint 2 documentacion/Sprint_02_Backlog_ICARO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentos Base\Sprint 2 documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55C382A-5CA9-4989-A360-1FB531A82254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26EC40A5-A9FE-4FF5-BB32-126132CA8191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Backlog Sprint 02" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="142">
   <si>
     <t>SPRINT BACKLOG — Sprint 02: Gestion de Proyectos, Avances de Obra y Evidencia Fotografica</t>
   </si>
@@ -120,9 +120,6 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>[Equipo]</t>
-  </si>
-  <si>
     <t>Completado</t>
   </si>
   <si>
@@ -439,13 +436,25 @@
   </si>
   <si>
     <t>34 SP / 1 semana</t>
+  </si>
+  <si>
+    <t>Isaac Sebastian Castro Muesmueran / Ivan Santiago Pulgar Leon</t>
+  </si>
+  <si>
+    <t>5/5</t>
+  </si>
+  <si>
+    <t>Todos los compromisos cumplidos</t>
+  </si>
+  <si>
+    <t>Compromisos Sprint 01 8.3 cumplidos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -511,6 +520,15 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="8">
@@ -602,7 +620,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -675,20 +693,32 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1025,7 +1055,7 @@
       <c r="L1" s="21"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="31" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="21"/>
@@ -1066,23 +1096,23 @@
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="30">
+      <c r="B4" s="28">
         <v>46132</v>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="32"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="30"/>
       <c r="G4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="30">
+      <c r="H4" s="28">
         <v>46136</v>
       </c>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="32"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="30"/>
     </row>
     <row r="5" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -1099,7 +1129,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I5" s="26"/>
       <c r="J5" s="26"/>
@@ -1188,34 +1218,34 @@
       <c r="G8" s="3">
         <v>8</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="I8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="J8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="K8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="L8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="L8" s="4" t="s">
+    </row>
+    <row r="9" spans="1:12" ht="139.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" ht="102.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>37</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>38</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>31</v>
@@ -1226,34 +1256,34 @@
       <c r="G9" s="6">
         <v>8</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I9" s="5" t="s">
-        <v>33</v>
-      </c>
       <c r="J9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="L9" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>31</v>
@@ -1264,31 +1294,31 @@
       <c r="G10" s="3">
         <v>5</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="I10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>33</v>
-      </c>
       <c r="J10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="K10" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="L10" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>30</v>
@@ -1302,34 +1332,34 @@
       <c r="G11" s="6">
         <v>5</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="I11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I11" s="5" t="s">
-        <v>33</v>
-      </c>
       <c r="J11" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="K11" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="K11" s="7" t="s">
+      <c r="L11" s="7" t="s">
         <v>52</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>56</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>31</v>
@@ -1340,37 +1370,37 @@
       <c r="G12" s="3">
         <v>5</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="I12" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="5" t="s">
-        <v>33</v>
-      </c>
       <c r="J12" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="K12" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="L12" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="C13" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>62</v>
       </c>
       <c r="F13" s="6">
         <v>3</v>
@@ -1378,25 +1408,25 @@
       <c r="G13" s="6">
         <v>3</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="I13" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I13" s="5" t="s">
-        <v>33</v>
-      </c>
       <c r="J13" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K13" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="K13" s="7" t="s">
+      <c r="L13" s="7" t="s">
         <v>64</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B14" s="23"/>
       <c r="C14" s="23"/>
@@ -1434,17 +1464,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
-        <v>67</v>
+      <c r="A1" s="32" t="s">
+        <v>66</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -1452,21 +1482,21 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="C2" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="D2" s="10" t="s">
         <v>70</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B3" s="12">
         <v>34</v>
@@ -1475,12 +1505,12 @@
         <v>34</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B4" s="15">
         <v>3</v>
@@ -1489,12 +1519,12 @@
         <v>3</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B5" s="12">
         <v>3</v>
@@ -1503,12 +1533,12 @@
         <v>3</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B6" s="15">
         <v>6</v>
@@ -1517,12 +1547,12 @@
         <v>6</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B7" s="12">
         <v>6</v>
@@ -1531,12 +1561,12 @@
         <v>6</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B8" s="15">
         <v>0</v>
@@ -1545,12 +1575,12 @@
         <v>0</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B9" s="12">
         <v>0</v>
@@ -1559,12 +1589,12 @@
         <v>0</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B10" s="15">
         <v>17</v>
@@ -1573,26 +1603,26 @@
         <v>17</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" s="13" t="s">
         <v>87</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B12" s="15">
         <v>17</v>
@@ -1601,21 +1631,35 @@
         <v>17</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>92</v>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="D14" s="36" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -1637,20 +1681,20 @@
   <sheetData>
     <row r="1" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="C2" s="10" t="s">
         <v>95</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1658,153 +1702,153 @@
         <v>29</v>
       </c>
       <c r="B3" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="18" t="s">
         <v>97</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="C5" s="18" t="s">
         <v>102</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="7" t="s">
         <v>105</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="C7" s="18" t="s">
         <v>108</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>111</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="C9" s="18" t="s">
         <v>114</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="C10" s="7" t="s">
         <v>117</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="B11" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="C11" s="18" t="s">
         <v>120</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="C12" s="7" t="s">
         <v>123</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="B13" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="C13" s="18" t="s">
         <v>126</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="C14" s="7" t="s">
         <v>129</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="B15" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="C15" s="18" t="s">
         <v>132</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="C16" s="7" t="s">
         <v>135</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/Documentos Base/Sprint 2 documentacion/Sprint_02_Backlog_ICARO.xlsx
+++ b/Documentos Base/Sprint 2 documentacion/Sprint_02_Backlog_ICARO.xlsx
@@ -1,28 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentos Base\Sprint 2 documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26EC40A5-A9FE-4FF5-BB32-126132CA8191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCF88412-2CA3-49BB-ADFF-934E37AD93A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Backlog Sprint 02" sheetId="1" r:id="rId1"/>
     <sheet name="Resumen Velocidad" sheetId="2" r:id="rId2"/>
-    <sheet name="Glosario" sheetId="3" r:id="rId3"/>
+    <sheet name="Resumen de Casos de Prueba" sheetId="4" r:id="rId3"/>
+    <sheet name="Glosario" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="209">
   <si>
     <t>SPRINT BACKLOG — Sprint 02: Gestion de Proyectos, Avances de Obra y Evidencia Fotografica</t>
   </si>
@@ -315,24 +316,12 @@
     <t>Historia de Usuario</t>
   </si>
   <si>
-    <t>Tipo de item del backlog orientado al usuario</t>
-  </si>
-  <si>
-    <t>Historia Tecnica</t>
-  </si>
-  <si>
-    <t>Tarea tecnica transversal del backlog</t>
-  </si>
-  <si>
     <t>SP</t>
   </si>
   <si>
     <t>Story Point</t>
   </si>
   <si>
-    <t>Unidad relativa de estimacion de esfuerzo</t>
-  </si>
-  <si>
     <t>RBAC</t>
   </si>
   <si>
@@ -348,45 +337,30 @@
     <t>JSON Web Token</t>
   </si>
   <si>
-    <t>Estandar de autenticacion firmado digitalmente</t>
-  </si>
-  <si>
     <t>CRUD</t>
   </si>
   <si>
     <t>Create, Read, Update, Delete</t>
   </si>
   <si>
-    <t>Operaciones basicas de gestion de datos</t>
-  </si>
-  <si>
     <t>API</t>
   </si>
   <si>
     <t>Application Programming Interface</t>
   </si>
   <si>
-    <t>Interfaz de programacion entre sistemas</t>
-  </si>
-  <si>
     <t>UUID</t>
   </si>
   <si>
     <t>Universally Unique Identifier</t>
   </si>
   <si>
-    <t>Identificador unico universal de entidades</t>
-  </si>
-  <si>
     <t>DoD</t>
   </si>
   <si>
     <t>Definition of Done</t>
   </si>
   <si>
-    <t>Criterios que definen un item como completado</t>
-  </si>
-  <si>
     <t>ORM</t>
   </si>
   <si>
@@ -405,33 +379,18 @@
     <t>Repositorio estructurado de datos del sistema</t>
   </si>
   <si>
-    <t>S3</t>
-  </si>
-  <si>
-    <t>Simple Storage Service</t>
-  </si>
-  <si>
-    <t>Servicio de almacenamiento en nube (AWS/extensible)</t>
-  </si>
-  <si>
     <t>BCK</t>
   </si>
   <si>
     <t>Backlog</t>
   </si>
   <si>
-    <t>Prefijo del codigo documental del Sprint Backlog</t>
-  </si>
-  <si>
     <t>SPR</t>
   </si>
   <si>
     <t>Sprint</t>
   </si>
   <si>
-    <t>Iteracion de desarrollo en metodologia Scrum</t>
-  </si>
-  <si>
     <t>Ivan Santiago Pulgar Leon</t>
   </si>
   <si>
@@ -448,13 +407,256 @@
   </si>
   <si>
     <t>Compromisos Sprint 01 8.3 cumplidos</t>
+  </si>
+  <si>
+    <t>Tipo de ítem del backlog orientado a funcionalidad</t>
+  </si>
+  <si>
+    <t>Historia Técnica</t>
+  </si>
+  <si>
+    <t>Tarea técnica transversal del equipo</t>
+  </si>
+  <si>
+    <t>Unidad relativa de estimación de esfuerzo</t>
+  </si>
+  <si>
+    <t>Estándar de autenticación firmado</t>
+  </si>
+  <si>
+    <t>Operaciones básicas de gestión</t>
+  </si>
+  <si>
+    <t>Interfaz de programación entre componentes</t>
+  </si>
+  <si>
+    <t>Identificador único universal para entidades</t>
+  </si>
+  <si>
+    <t>Criterios que definen un ítem como completado</t>
+  </si>
+  <si>
+    <t>Prefijo del código documental del backlog</t>
+  </si>
+  <si>
+    <t>Iteración de desarrollo en metodología Scrum</t>
+  </si>
+  <si>
+    <t>PLN-REA</t>
+  </si>
+  <si>
+    <t>Planificado-Realizado</t>
+  </si>
+  <si>
+    <t>Documento de comparación de sprint</t>
+  </si>
+  <si>
+    <t>INF-PRU</t>
+  </si>
+  <si>
+    <t>Informe de Pruebas</t>
+  </si>
+  <si>
+    <t>Documento de resultados de pruebas del sprint</t>
+  </si>
+  <si>
+    <t>RESUMEN DE CASOS DE PRUEBA — SPRINT 07 (CP-123 a CP-168)</t>
+  </si>
+  <si>
+    <t>ID CP</t>
+  </si>
+  <si>
+    <t>Grupo</t>
+  </si>
+  <si>
+    <t>Módulo</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Evidencia</t>
+  </si>
+  <si>
+    <t>Grupo 1</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>Grupo 2</t>
+  </si>
+  <si>
+    <t>Grupo 3</t>
+  </si>
+  <si>
+    <t>CP-016</t>
+  </si>
+  <si>
+    <t>Gestión de Proyectos</t>
+  </si>
+  <si>
+    <t>GET /proyectos sin token → 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>proyectos_avances.test.js – Test 01</t>
+  </si>
+  <si>
+    <t>CP-017</t>
+  </si>
+  <si>
+    <t>GET /proyectos con token Admin → pasa autenticación y RBAC</t>
+  </si>
+  <si>
+    <t>proyectos_avances.test.js – Test 02</t>
+  </si>
+  <si>
+    <t>CP-018</t>
+  </si>
+  <si>
+    <t>GET /proyectos con token Residente → pasa autenticación y RBAC</t>
+  </si>
+  <si>
+    <t>proyectos_avances.test.js – Test 03</t>
+  </si>
+  <si>
+    <t>CP-019</t>
+  </si>
+  <si>
+    <t>POST /proyectos sin token → 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>proyectos_avances.test.js – Test 04</t>
+  </si>
+  <si>
+    <t>CP-020</t>
+  </si>
+  <si>
+    <t>POST /proyectos con rol Residente → 403 Forbidden</t>
+  </si>
+  <si>
+    <t>proyectos_avances.test.js – Test 05</t>
+  </si>
+  <si>
+    <t>CP-021</t>
+  </si>
+  <si>
+    <t>GET /proyectos/:id sin token → 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>proyectos_avances.test.js – Test 06</t>
+  </si>
+  <si>
+    <t>CP-022</t>
+  </si>
+  <si>
+    <t>GET /proyectos/:id con token Admin → pasa autenticación y RBAC</t>
+  </si>
+  <si>
+    <t>proyectos_avances.test.js – Test 07</t>
+  </si>
+  <si>
+    <t>CP-023</t>
+  </si>
+  <si>
+    <t>Avances de Obra</t>
+  </si>
+  <si>
+    <t>POST /avances sin token → 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>proyectos_avances.test.js – Test 08</t>
+  </si>
+  <si>
+    <t>CP-024</t>
+  </si>
+  <si>
+    <t>POST /avances con rol Contador → 403 Forbidden</t>
+  </si>
+  <si>
+    <t>proyectos_avances.test.js – Test 09</t>
+  </si>
+  <si>
+    <t>CP-025</t>
+  </si>
+  <si>
+    <t>POST /avances con rol Bodeguero → 403 Forbidden</t>
+  </si>
+  <si>
+    <t>proyectos_avances.test.js – Test 10</t>
+  </si>
+  <si>
+    <t>CP-026</t>
+  </si>
+  <si>
+    <t>POST /avances con Residente sin evidencia fotográfica → 400, evidencia obligatoria</t>
+  </si>
+  <si>
+    <t>proyectos_avances.test.js – Test 11</t>
+  </si>
+  <si>
+    <t>CP-027</t>
+  </si>
+  <si>
+    <t>POST /avances con Admin sin evidencia → 400, evidencia obligatoria para todos los roles</t>
+  </si>
+  <si>
+    <t>proyectos_avances.test.js – Test 12</t>
+  </si>
+  <si>
+    <t>CP-028</t>
+  </si>
+  <si>
+    <t>GET /avances/rubro/:idRubro sin token → 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>proyectos_avances.test.js – Test 13</t>
+  </si>
+  <si>
+    <t>CP-029</t>
+  </si>
+  <si>
+    <t>GET /avances/rubro/:idRubro con token Admin → pasa autenticación y RBAC</t>
+  </si>
+  <si>
+    <t>proyectos_avances.test.js – Test 14</t>
+  </si>
+  <si>
+    <t>CP-030</t>
+  </si>
+  <si>
+    <t>Carga Masiva de Rubros</t>
+  </si>
+  <si>
+    <t>POST /proyectos/:id/rubros/bulk sin token → 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>proyectos_avances.test.js – Test 15</t>
+  </si>
+  <si>
+    <t>CP-031</t>
+  </si>
+  <si>
+    <t>POST /proyectos/:id/rubros/bulk con Residente → 403 Forbidden</t>
+  </si>
+  <si>
+    <t>proyectos_avances.test.js – Test 16</t>
+  </si>
+  <si>
+    <t>CP-032</t>
+  </si>
+  <si>
+    <t>POST /proyectos/:id/rubros/bulk con Admin → pasa RBAC</t>
+  </si>
+  <si>
+    <t>proyectos_avances.test.js – Test 17</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -524,11 +726,35 @@
     <font>
       <sz val="9"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1F3864"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -569,7 +795,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -616,11 +842,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -668,16 +924,19 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -705,20 +964,50 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1039,124 +1328,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
     </row>
     <row r="3" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="28"/>
       <c r="G3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="25" t="s">
+      <c r="H3" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="28"/>
     </row>
     <row r="4" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="28">
+      <c r="B4" s="29">
         <v>46132</v>
       </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="31"/>
       <c r="G4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="29">
         <v>46136</v>
       </c>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="31"/>
     </row>
     <row r="5" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="28"/>
       <c r="G5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="27"/>
+      <c r="H5" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="28"/>
     </row>
     <row r="6" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="28"/>
       <c r="G6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="25" t="s">
+      <c r="H6" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="28"/>
     </row>
     <row r="7" spans="1:12" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
@@ -1218,8 +1507,8 @@
       <c r="G8" s="3">
         <v>8</v>
       </c>
-      <c r="H8" s="33" t="s">
-        <v>138</v>
+      <c r="H8" s="17" t="s">
+        <v>124</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>32</v>
@@ -1256,8 +1545,8 @@
       <c r="G9" s="6">
         <v>8</v>
       </c>
-      <c r="H9" s="33" t="s">
-        <v>138</v>
+      <c r="H9" s="17" t="s">
+        <v>124</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>32</v>
@@ -1294,8 +1583,8 @@
       <c r="G10" s="3">
         <v>5</v>
       </c>
-      <c r="H10" s="33" t="s">
-        <v>138</v>
+      <c r="H10" s="17" t="s">
+        <v>124</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>32</v>
@@ -1332,8 +1621,8 @@
       <c r="G11" s="6">
         <v>5</v>
       </c>
-      <c r="H11" s="33" t="s">
-        <v>138</v>
+      <c r="H11" s="17" t="s">
+        <v>124</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>32</v>
@@ -1370,8 +1659,8 @@
       <c r="G12" s="3">
         <v>5</v>
       </c>
-      <c r="H12" s="33" t="s">
-        <v>138</v>
+      <c r="H12" s="17" t="s">
+        <v>124</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>32</v>
@@ -1408,8 +1697,8 @@
       <c r="G13" s="6">
         <v>3</v>
       </c>
-      <c r="H13" s="33" t="s">
-        <v>138</v>
+      <c r="H13" s="17" t="s">
+        <v>124</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>32</v>
@@ -1425,13 +1714,13 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
       <c r="F14" s="9">
         <v>34</v>
       </c>
@@ -1473,12 +1762,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -1603,7 +1892,7 @@
         <v>17</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1649,17 +1938,17 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="34" t="s">
-        <v>141</v>
-      </c>
-      <c r="B14" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="C14" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="D14" s="36" t="s">
-        <v>140</v>
+      <c r="A14" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -1671,8 +1960,506 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D883E32-42DC-4ADA-AC40-8F15334F68E0}">
+  <dimension ref="A1:M19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" customWidth="1"/>
+    <col min="4" max="4" width="75.85546875" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="45" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="40" t="s">
+        <v>146</v>
+      </c>
+      <c r="B2" s="40" t="s">
+        <v>147</v>
+      </c>
+      <c r="C2" s="40" t="s">
+        <v>148</v>
+      </c>
+      <c r="D2" s="40" t="s">
+        <v>149</v>
+      </c>
+      <c r="E2" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="41" t="s">
+        <v>155</v>
+      </c>
+      <c r="B3" s="41" t="s">
+        <v>151</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="E3" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="F3" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="44" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" s="44" t="s">
+        <v>151</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>156</v>
+      </c>
+      <c r="D4" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="E4" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="F4" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="41" t="s">
+        <v>162</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="D5" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="E5" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="F5" s="42" t="s">
+        <v>164</v>
+      </c>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="47"/>
+      <c r="K5" s="47"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="47"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="44" t="s">
+        <v>165</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>151</v>
+      </c>
+      <c r="C6" s="44" t="s">
+        <v>156</v>
+      </c>
+      <c r="D6" s="45" t="s">
+        <v>166</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="F6" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="47"/>
+      <c r="K6" s="47"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="47"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="41" t="s">
+        <v>168</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>151</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>169</v>
+      </c>
+      <c r="E7" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="F7" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="H7" s="47"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="47"/>
+      <c r="K7" s="47"/>
+      <c r="L7" s="47"/>
+      <c r="M7" s="47"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="44" t="s">
+        <v>171</v>
+      </c>
+      <c r="B8" s="44" t="s">
+        <v>151</v>
+      </c>
+      <c r="C8" s="44" t="s">
+        <v>156</v>
+      </c>
+      <c r="D8" s="45" t="s">
+        <v>172</v>
+      </c>
+      <c r="E8" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="F8" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="H8" s="47"/>
+      <c r="I8" s="47"/>
+      <c r="J8" s="47"/>
+      <c r="K8" s="47"/>
+      <c r="L8" s="47"/>
+      <c r="M8" s="47"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="41" t="s">
+        <v>174</v>
+      </c>
+      <c r="B9" s="41" t="s">
+        <v>151</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="D9" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="F9" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="47"/>
+      <c r="K9" s="47"/>
+      <c r="L9" s="47"/>
+      <c r="M9" s="47"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>153</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="D10" s="45" t="s">
+        <v>179</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="F10" s="45" t="s">
+        <v>180</v>
+      </c>
+      <c r="H10" s="47"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="47"/>
+      <c r="K10" s="47"/>
+      <c r="L10" s="47"/>
+      <c r="M10" s="47"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="41" t="s">
+        <v>181</v>
+      </c>
+      <c r="B11" s="41" t="s">
+        <v>153</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="D11" s="42" t="s">
+        <v>182</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="F11" s="42" t="s">
+        <v>183</v>
+      </c>
+      <c r="H11" s="47"/>
+      <c r="I11" s="47"/>
+      <c r="J11" s="47"/>
+      <c r="K11" s="47"/>
+      <c r="L11" s="47"/>
+      <c r="M11" s="47"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="44" t="s">
+        <v>184</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>153</v>
+      </c>
+      <c r="C12" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="D12" s="45" t="s">
+        <v>185</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="F12" s="45" t="s">
+        <v>186</v>
+      </c>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="47"/>
+      <c r="K12" s="47"/>
+      <c r="L12" s="47"/>
+      <c r="M12" s="47"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="41" t="s">
+        <v>187</v>
+      </c>
+      <c r="B13" s="41" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="D13" s="42" t="s">
+        <v>188</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="F13" s="42" t="s">
+        <v>189</v>
+      </c>
+      <c r="H13" s="47"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="47"/>
+      <c r="K13" s="47"/>
+      <c r="L13" s="47"/>
+      <c r="M13" s="47"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="44" t="s">
+        <v>190</v>
+      </c>
+      <c r="B14" s="44" t="s">
+        <v>153</v>
+      </c>
+      <c r="C14" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="D14" s="45" t="s">
+        <v>191</v>
+      </c>
+      <c r="E14" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="F14" s="45" t="s">
+        <v>192</v>
+      </c>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="47"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="47"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="41" t="s">
+        <v>193</v>
+      </c>
+      <c r="B15" s="41" t="s">
+        <v>153</v>
+      </c>
+      <c r="C15" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="D15" s="42" t="s">
+        <v>194</v>
+      </c>
+      <c r="E15" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="F15" s="42" t="s">
+        <v>195</v>
+      </c>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="47"/>
+      <c r="K15" s="47"/>
+      <c r="L15" s="47"/>
+      <c r="M15" s="47"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="B16" s="44" t="s">
+        <v>153</v>
+      </c>
+      <c r="C16" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="D16" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="F16" s="45" t="s">
+        <v>198</v>
+      </c>
+      <c r="H16" s="47"/>
+      <c r="I16" s="47"/>
+      <c r="J16" s="47"/>
+      <c r="K16" s="47"/>
+      <c r="L16" s="47"/>
+      <c r="M16" s="47"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="41" t="s">
+        <v>199</v>
+      </c>
+      <c r="B17" s="41" t="s">
+        <v>154</v>
+      </c>
+      <c r="C17" s="41" t="s">
+        <v>200</v>
+      </c>
+      <c r="D17" s="42" t="s">
+        <v>201</v>
+      </c>
+      <c r="E17" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="F17" s="42" t="s">
+        <v>202</v>
+      </c>
+      <c r="H17" s="47"/>
+      <c r="I17" s="47"/>
+      <c r="J17" s="47"/>
+      <c r="K17" s="47"/>
+      <c r="L17" s="47"/>
+      <c r="M17" s="47"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="44" t="s">
+        <v>203</v>
+      </c>
+      <c r="B18" s="44" t="s">
+        <v>154</v>
+      </c>
+      <c r="C18" s="44" t="s">
+        <v>200</v>
+      </c>
+      <c r="D18" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="E18" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="F18" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="47"/>
+      <c r="K18" s="47"/>
+      <c r="L18" s="47"/>
+      <c r="M18" s="47"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="41" t="s">
+        <v>206</v>
+      </c>
+      <c r="B19" s="41" t="s">
+        <v>154</v>
+      </c>
+      <c r="C19" s="41" t="s">
+        <v>200</v>
+      </c>
+      <c r="D19" s="42" t="s">
+        <v>207</v>
+      </c>
+      <c r="E19" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="F19" s="42" t="s">
+        <v>208</v>
+      </c>
+      <c r="H19" s="47"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="47"/>
+      <c r="K19" s="47"/>
+      <c r="L19" s="47"/>
+      <c r="M19" s="47"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1680,175 +2467,186 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="34" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="36" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="38" t="s">
+        <v>129</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="35" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="B5" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C5" s="36" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="37" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+      <c r="B6" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="C6" s="38" t="s">
         <v>101</v>
       </c>
-      <c r="C5" s="18" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="35" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+      <c r="B7" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C7" s="36" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="B8" s="38" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="C8" s="38" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B9" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C9" s="36" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="37" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="B10" s="38" t="s">
         <v>109</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="C10" s="38" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="35" t="s">
         <v>110</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="B11" s="36" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+      <c r="C11" s="36" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="37" t="s">
         <v>112</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B12" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C12" s="38" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="35" t="s">
         <v>115</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B13" s="36" t="s">
         <v>116</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C13" s="36" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="37" t="s">
         <v>118</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B14" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C14" s="38" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="35" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+      <c r="B15" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>132</v>
+      <c r="C15" s="36" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>135</v>
+      <c r="A16" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="B16" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="B17" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
